--- a/Libraries/Vehicle/Suspension/AxleTA3/sm_car_data_Linkage_AxleTA3.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA3/sm_car_data_Linkage_AxleTA3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705C96A0-8D52-4186-B972-18E5C8CD6799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D8F114-219F-4A78-B129-9296B360C974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11235" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA3_SUV_Landy_r" sheetId="5" r:id="rId1"/>
@@ -717,7 +717,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -731,7 +731,7 @@
     <col min="11" max="13" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -751,7 +751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -765,7 +765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -777,7 +777,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>45</v>
       </c>
@@ -809,7 +809,7 @@
       </c>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>39</v>
@@ -824,17 +824,26 @@
         <v>25</v>
       </c>
       <c r="F6" s="10">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="K6" s="10">
         <f>2.8-2.0282</f>
         <v>0.77179999999999982</v>
       </c>
-      <c r="G6" s="10">
+      <c r="L6" s="10">
         <v>0.44600000000000001</v>
       </c>
-      <c r="H6" s="10">
+      <c r="M6" s="10">
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
@@ -847,18 +856,27 @@
         <v>26</v>
       </c>
       <c r="F7" s="10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="K7" s="10">
         <f>2.8-2.839</f>
         <v>-3.9000000000000146E-2</v>
       </c>
-      <c r="G7" s="10">
+      <c r="L7" s="10">
         <f>0.4525</f>
         <v>0.45250000000000001</v>
       </c>
-      <c r="H7" s="10">
+      <c r="M7" s="10">
         <v>0.315</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9" t="s">
@@ -870,10 +888,10 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
         <v>47</v>
@@ -888,17 +906,26 @@
         <v>27</v>
       </c>
       <c r="F9" s="10">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="K9" s="10">
         <f>2.8-2.3062</f>
         <v>0.49379999999999979</v>
       </c>
-      <c r="G9" s="10">
+      <c r="L9" s="10">
         <v>0.22</v>
       </c>
-      <c r="H9" s="10">
+      <c r="M9" s="10">
         <v>0.52400000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9" t="s">
@@ -911,17 +938,26 @@
         <v>28</v>
       </c>
       <c r="F10" s="10">
+        <v>-0.04</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="K10" s="10">
         <f>2.8-2.794</f>
         <v>5.9999999999997833E-3</v>
       </c>
-      <c r="G10" s="10">
+      <c r="L10" s="10">
         <v>0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="M10" s="10">
         <v>0.51700000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9" t="s">
@@ -933,10 +969,10 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
         <v>21</v>
@@ -953,11 +989,11 @@
       <c r="F12" s="12"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10">
-        <v>143</v>
+        <v>168.5</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
@@ -973,11 +1009,20 @@
         <v>0</v>
       </c>
       <c r="H13" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
         <v>0.38</v>
       </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
         <v>55</v>
@@ -993,7 +1038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="s">
@@ -1011,8 +1056,11 @@
       <c r="H15" s="10">
         <v>0.438</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
@@ -1030,8 +1078,11 @@
       <c r="H16" s="10">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
@@ -1046,7 +1097,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
@@ -1070,7 +1121,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
@@ -1085,7 +1136,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
@@ -1100,7 +1151,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
@@ -1115,7 +1166,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>34</v>
@@ -1137,11 +1188,21 @@
         <v>0.62544999999999995</v>
       </c>
       <c r="H22" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="12">
+        <f>2.8-2.8</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0.62544999999999995</v>
+      </c>
+      <c r="M22" s="10">
         <v>0.38</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
@@ -1151,14 +1212,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="23">
-        <f>2.8-2.9586</f>
-        <v>-0.1586000000000003</v>
+        <v>-0.16600000000000001</v>
       </c>
       <c r="G23" s="23">
-        <v>0.61470000000000002</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="H23" s="23">
-        <v>0.30499999999999999</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="J23" s="24" t="s">
         <v>48</v>
@@ -1168,7 +1228,7 @@
       <c r="M23" s="24"/>
       <c r="N23" s="24"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
@@ -1187,10 +1247,19 @@
         <v>0.74295</v>
       </c>
       <c r="H24" s="10">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.74295</v>
+      </c>
+      <c r="M24" s="10">
         <v>0.38</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
@@ -1208,7 +1277,7 @@
         <v>-3.25</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
@@ -1226,7 +1295,7 @@
         <v>7.0110000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
@@ -1245,7 +1314,7 @@
       </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8" t="s">
         <v>29</v>
@@ -1260,18 +1329,27 @@
         <v>30</v>
       </c>
       <c r="F28" s="22">
+        <v>-0.191</v>
+      </c>
+      <c r="G28" s="22">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="H28" s="22">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="22">
         <f>2.8-2.9586</f>
         <v>-0.1586000000000003</v>
       </c>
-      <c r="G28" s="22">
+      <c r="L28" s="22">
         <v>0.61470000000000002</v>
       </c>
-      <c r="H28" s="22">
+      <c r="M28" s="22">
         <v>0.30499999999999999</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9" t="s">
@@ -1286,7 +1364,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="13" t="s">
         <v>11</v>
@@ -1301,14 +1379,13 @@
         <v>24</v>
       </c>
       <c r="F30" s="20">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G30" s="20">
-        <v>0.48549999999999999</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="H30" s="20">
-        <v>0.67633500000000002</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>32</v>
@@ -1318,8 +1395,18 @@
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
       <c r="O30" s="14"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q30" s="20">
+        <f>2.8-2.79</f>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="R30" s="20">
+        <v>0.48549999999999999</v>
+      </c>
+      <c r="S30" s="20">
+        <v>0.67633500000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="s">
@@ -1332,14 +1419,13 @@
         <v>23</v>
       </c>
       <c r="F31" s="20">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G31" s="20">
-        <v>0.48549999999999999</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H31" s="20">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="J31" s="14" t="s">
         <v>32</v>
@@ -1349,8 +1435,18 @@
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q31" s="20">
+        <f>2.8-2.79</f>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="R31" s="20">
+        <v>0.48549999999999999</v>
+      </c>
+      <c r="S31" s="20">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">
@@ -1365,7 +1461,7 @@
         <v>3.6529410000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
@@ -1380,7 +1476,7 @@
         <v>4.3157700000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="15" t="s">
         <v>16</v>
@@ -1394,7 +1490,7 @@
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="19">
-        <v>0.13500000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="J34" s="16" t="s">
         <v>33</v>
@@ -1403,8 +1499,11 @@
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P34">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
       <c r="B35" s="15"/>
       <c r="C35" s="16" t="s">
@@ -1416,7 +1515,7 @@
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="19">
-        <v>-0.115</v>
+        <v>-0.158</v>
       </c>
       <c r="J35" s="16" t="s">
         <v>33</v>
@@ -1425,8 +1524,11 @@
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P35">
+        <v>-0.115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>40</v>
@@ -1442,7 +1544,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>44</v>

--- a/Libraries/Vehicle/Suspension/AxleTA3/sm_car_data_Linkage_AxleTA3.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA3/sm_car_data_Linkage_AxleTA3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D8F114-219F-4A78-B129-9296B360C974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F2AB3B-802C-44A2-94F0-5176AEA11EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="11760" yWindow="930" windowWidth="20910" windowHeight="13860" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA3_SUV_Landy_r" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
   <si>
     <t>Units</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>Bumpstop</t>
-  </si>
-  <si>
-    <t>sChassis</t>
   </si>
   <si>
     <t>xHeight</t>
@@ -319,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -357,14 +354,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,7 +715,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="17" customWidth="1"/>
@@ -823,25 +821,18 @@
       <c r="E6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="10">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="K6" s="10">
-        <f>2.8-2.0282</f>
-        <v>0.77179999999999982</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0.39500000000000002</v>
-      </c>
+      <c r="F6" s="18">
+        <v>0.77</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
@@ -855,26 +846,18 @@
       <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="10">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0.33600000000000002</v>
-      </c>
-      <c r="K7" s="10">
-        <f>2.8-2.839</f>
-        <v>-3.9000000000000146E-2</v>
-      </c>
-      <c r="L7" s="10">
-        <f>0.4525</f>
-        <v>0.45250000000000001</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0.315</v>
-      </c>
+      <c r="F7" s="18">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0.4425</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
@@ -905,25 +888,18 @@
       <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="10">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="K9" s="10">
-        <f>2.8-2.3062</f>
-        <v>0.49379999999999979</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0.52400000000000002</v>
-      </c>
+      <c r="F9" s="18">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0.245</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
@@ -937,25 +913,18 @@
       <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="10">
-        <v>-0.04</v>
-      </c>
-      <c r="G10" s="10">
+      <c r="F10" s="18">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G10" s="18">
         <v>0</v>
       </c>
-      <c r="H10" s="10">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="K10" s="10">
-        <f>2.8-2.794</f>
-        <v>5.9999999999997833E-3</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="10">
-        <v>0.51700000000000002</v>
-      </c>
+      <c r="H10" s="18">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
@@ -1002,25 +971,19 @@
       <c r="D13" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="18">
         <v>0</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="18">
         <v>0</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="18">
         <v>0.38800000000000001</v>
       </c>
       <c r="J13" s="18"/>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0.38</v>
-      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
@@ -1034,8 +997,8 @@
       <c r="E14" s="5"/>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="21" t="s">
-        <v>64</v>
+      <c r="H14" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1047,14 +1010,14 @@
       <c r="D15" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="18">
         <v>0</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="18">
         <v>0</v>
       </c>
-      <c r="H15" s="10">
-        <v>0.438</v>
+      <c r="H15" s="18">
+        <v>0.45800000000000002</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
@@ -1064,29 +1027,29 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="18">
         <v>0</v>
       </c>
-      <c r="G16" s="10">
-        <v>0.35749999999999998</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.51</v>
+      <c r="G16" s="18">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H16" s="18">
+        <v>0.61199999999999999</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -1097,17 +1060,17 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -1121,14 +1084,14 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
         <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -1136,14 +1099,14 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -1151,11 +1114,11 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
@@ -1166,7 +1129,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>34</v>
@@ -1180,29 +1143,21 @@
       <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="12">
-        <f>2.8-2.8</f>
+      <c r="F22" s="18">
         <v>0</v>
       </c>
-      <c r="G22" s="10">
-        <v>0.62544999999999995</v>
-      </c>
-      <c r="H22" s="10">
-        <v>0.38800000000000001</v>
+      <c r="G22" s="18">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="H22" s="18">
+        <v>0.40100000000000002</v>
       </c>
       <c r="J22" s="18"/>
-      <c r="K22" s="12">
-        <f>2.8-2.8</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="10">
-        <v>0.62544999999999995</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K22" s="12"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
@@ -1211,24 +1166,24 @@
       <c r="D23" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="23">
-        <v>-0.16600000000000001</v>
-      </c>
-      <c r="G23" s="23">
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="H23" s="23">
-        <v>0.27400000000000002</v>
-      </c>
-      <c r="J23" s="24" t="s">
+      <c r="F23" s="22">
+        <v>-0.126</v>
+      </c>
+      <c r="G23" s="22">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H23" s="22">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="J23" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
@@ -1240,26 +1195,20 @@
       <c r="E24" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="18">
         <v>0</v>
       </c>
-      <c r="G24" s="10">
-        <v>0.74295</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="K24" s="10">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10">
-        <v>0.74295</v>
-      </c>
-      <c r="M24" s="10">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="G24" s="18">
+        <v>0.754</v>
+      </c>
+      <c r="H24" s="18">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9" t="s">
@@ -1277,7 +1226,7 @@
         <v>-3.25</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9" t="s">
@@ -1295,7 +1244,7 @@
         <v>7.0110000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
@@ -1314,7 +1263,7 @@
       </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8" t="s">
         <v>29</v>
@@ -1328,28 +1277,21 @@
       <c r="E28" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="22">
-        <v>-0.191</v>
-      </c>
-      <c r="G28" s="22">
-        <v>0.61899999999999999</v>
-      </c>
-      <c r="H28" s="22">
-        <v>0.33400000000000002</v>
+      <c r="F28" s="23">
+        <v>-0.16</v>
+      </c>
+      <c r="G28" s="23">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="H28" s="23">
+        <v>0.311</v>
       </c>
       <c r="J28" s="18"/>
-      <c r="K28" s="22">
-        <f>2.8-2.9586</f>
-        <v>-0.1586000000000003</v>
-      </c>
-      <c r="L28" s="22">
-        <v>0.61470000000000002</v>
-      </c>
-      <c r="M28" s="22">
-        <v>0.30499999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9" t="s">
@@ -1364,7 +1306,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="13" t="s">
         <v>11</v>
@@ -1378,14 +1320,14 @@
       <c r="E30" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="20">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0.73899999999999999</v>
+      <c r="F30" s="24">
+        <v>2E-3</v>
+      </c>
+      <c r="G30" s="24">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="H30" s="24">
+        <v>0.80200000000000005</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>32</v>
@@ -1395,18 +1337,8 @@
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
       <c r="O30" s="14"/>
-      <c r="Q30" s="20">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
-      </c>
-      <c r="R30" s="20">
-        <v>0.48549999999999999</v>
-      </c>
-      <c r="S30" s="20">
-        <v>0.67633500000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="s">
@@ -1418,14 +1350,14 @@
       <c r="E31" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="20">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="G31" s="20">
+      <c r="F31" s="24">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G31" s="24">
         <v>0.54300000000000004</v>
       </c>
-      <c r="H31" s="20">
-        <v>0.53</v>
+      <c r="H31" s="24">
+        <v>0.57299999999999995</v>
       </c>
       <c r="J31" s="14" t="s">
         <v>32</v>
@@ -1435,18 +1367,8 @@
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
-      <c r="Q31" s="20">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
-      </c>
-      <c r="R31" s="20">
-        <v>0.48549999999999999</v>
-      </c>
-      <c r="S31" s="20">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="9" t="s">
@@ -1461,7 +1383,7 @@
         <v>3.6529410000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9" t="s">
@@ -1476,7 +1398,7 @@
         <v>4.3157700000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="15" t="s">
         <v>16</v>
@@ -1489,8 +1411,9 @@
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
-      <c r="H34" s="19">
-        <v>0.14199999999999999</v>
+      <c r="H34" s="25">
+        <f>0.3+H35</f>
+        <v>0.11499999999999999</v>
       </c>
       <c r="J34" s="16" t="s">
         <v>33</v>
@@ -1499,11 +1422,8 @@
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
-      <c r="P34">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
       <c r="B35" s="15"/>
       <c r="C35" s="16" t="s">
@@ -1514,8 +1434,8 @@
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
-      <c r="H35" s="19">
-        <v>-0.158</v>
+      <c r="H35" s="25">
+        <v>-0.185</v>
       </c>
       <c r="J35" s="16" t="s">
         <v>33</v>
@@ -1524,11 +1444,8 @@
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
-      <c r="P35">
-        <v>-0.115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>40</v>
@@ -1540,11 +1457,11 @@
       <c r="E36" s="5"/>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>44</v>
@@ -1556,7 +1473,7 @@
       <c r="E37" s="5"/>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="19" t="s">
         <v>43</v>
       </c>
     </row>
